--- a/ExpresswayBSSs_v2/data/data_generation_rl/3s6e_station__price_info.xlsx
+++ b/ExpresswayBSSs_v2/data/data_generation_rl/3s6e_station__price_info.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\17280\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Myfiles\vscode_files\cleanrl_BSS\ExpresswayBSSs_v2\data\data_generation_rl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771D2D3B-D30F-462F-923D-170679478392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E803E04F-5583-4494-8FD7-8B27C5EF5F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="1920" windowWidth="27255" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -395,17 +395,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD6"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -497,7 +497,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -589,7 +589,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -681,7 +681,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -773,10 +773,10 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
     </row>
   </sheetData>
